--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-02T12:40:26+00:00</t>
+    <t>2026-01-05T09:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-05T09:23:02+00:00</t>
+    <t>2026-01-05T14:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-05T14:58:24+00:00</t>
+    <t>2026-01-07T08:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T08:10:47+00:00</t>
+    <t>2026-01-07T08:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T08:12:12+00:00</t>
+    <t>2026-01-07T08:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T08:28:56+00:00</t>
+    <t>2026-01-07T08:31:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T08:31:17+00:00</t>
+    <t>2026-01-07T08:31:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T08:31:16+00:00</t>
+    <t>2026-01-07T08:35:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T08:35:03+00:00</t>
+    <t>2026-01-07T10:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:40:47+00:00</t>
+    <t>2026-01-07T10:42:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:42:26+00:00</t>
+    <t>2026-01-08T14:03:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>6.0.0-rc</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-08T14:03:32+00:00</t>
+    <t>2026-01-08T14:46:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-08T14:46:36+00:00</t>
+    <t>2026-01-08T15:18:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-08T15:18:36+00:00</t>
+    <t>2026-01-09T07:37:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-09T07:37:22+00:00</t>
+    <t>2026-01-09T09:42:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-09T09:42:04+00:00</t>
+    <t>2026-01-09T12:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-09T12:51:52+00:00</t>
+    <t>2026-01-12T08:08:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
